--- a/data/profile.xlsx
+++ b/data/profile.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Ahmed\09 Other\portfolio\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Makled\Desktop\portfolio, cv\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2654008-75F8-434F-916F-8676311BE10F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7923465-5D5E-42DC-8A5F-445B0FE6DB80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="23">
   <si>
     <t>Name</t>
   </si>
@@ -66,9 +66,6 @@
     <t>assets/images/profile.jpg</t>
   </si>
   <si>
-    <t>I'm a professional Flutter Mobile Developer specialized in building high-quality Android applications using Flutter, Firebase, and REST APIs. I focus on creating reliable real-world solutions through clean architecture and maintainable code. I have built and maintained 100+ screens and 10+ production-ready applications from concept to deployment.</t>
-  </si>
-  <si>
     <t>ahmed1.makled1@gmail.com</t>
   </si>
   <si>
@@ -78,9 +75,6 @@
     <t>Egypt</t>
   </si>
   <si>
-    <t>assets/cv/Ahmed_Makled_CV.pdf</t>
-  </si>
-  <si>
     <t>v1.0</t>
   </si>
   <si>
@@ -88,6 +82,18 @@
   </si>
   <si>
     <t>Ahmed Nasr Makled</t>
+  </si>
+  <si>
+    <t>assets/cv/Ahmed Nasr Ahmed Makled CV.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Description </t>
+  </si>
+  <si>
+    <t>I build scalable, high-performance cross-platform mobile applications using Flutter, Dart, Firebase, and REST APIs. Passionate about clean architecture, maintainable code, and delivering production-ready solutions that provide exceptional user experiences.</t>
+  </si>
+  <si>
+    <t>I'm a Flutter Mobile Application Developer with a Bachelor's degree in Computer Science and Artificial Intelligence, specializing in Information Technology. I enjoy transforming ideas into reliable, production-ready mobile applications by applying Clean Architecture, SOLID principles, and modern development practices. Through professional training at the Digital Egypt Pioneers Initiative (DEPI) and the National Telecommunication Institute (NTI), I've gained hands-on experience developing scalable Flutter applications, integrating Firebase and REST APIs, and collaborating with teams using Git and agile workflows. I've built and maintained 10+ production-ready applications, developed 100+ responsive mobile screens, and integrated 50+ backend APIs. I'm passionate about writing clean, maintainable code and continuously learning new technologies to create software that solves real-world problems.</t>
   </si>
 </sst>
 </file>
@@ -123,8 +129,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -427,13 +436,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:L10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="36" customWidth="1"/>
+    <col min="1" max="1" width="19.7109375" customWidth="1"/>
+    <col min="2" max="3" width="32.28515625" customWidth="1"/>
+    <col min="4" max="4" width="25.42578125" customWidth="1"/>
+    <col min="5" max="6" width="28.140625" customWidth="1"/>
+    <col min="7" max="7" width="14.140625" customWidth="1"/>
+    <col min="8" max="8" width="13" customWidth="1"/>
+    <col min="9" max="9" width="7.85546875" customWidth="1"/>
+    <col min="10" max="10" width="41.140625" customWidth="1"/>
+    <col min="11" max="11" width="9.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -441,67 +458,76 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B2" t="s">
         <v>11</v>
       </c>
       <c r="C2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D2" t="s">
         <v>12</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F2" t="s">
         <v>13</v>
       </c>
-      <c r="E2" t="s">
+      <c r="G2" t="s">
         <v>14</v>
       </c>
-      <c r="F2" t="s">
+      <c r="H2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I2" t="s">
         <v>15</v>
       </c>
-      <c r="G2" t="s">
-        <v>15</v>
-      </c>
-      <c r="H2" t="s">
+      <c r="J2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2" t="s">
         <v>16</v>
       </c>
-      <c r="I2" t="s">
+      <c r="L2" t="s">
         <v>17</v>
       </c>
-      <c r="J2" t="s">
-        <v>18</v>
-      </c>
-      <c r="K2" t="s">
-        <v>19</v>
-      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="E10" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/profile.xlsx
+++ b/data/profile.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Makled\Desktop\portfolio, cv\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Ahmed\05 Enhance Work\portfolio\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7923465-5D5E-42DC-8A5F-445B0FE6DB80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E0E1C03-2AEA-44BC-8248-B720BBE966FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -84,9 +84,6 @@
     <t>Ahmed Nasr Makled</t>
   </si>
   <si>
-    <t>assets/cv/Ahmed Nasr Ahmed Makled CV.pdf</t>
-  </si>
-  <si>
     <t xml:space="preserve">Description </t>
   </si>
   <si>
@@ -94,6 +91,9 @@
   </si>
   <si>
     <t>I'm a Flutter Mobile Application Developer with a Bachelor's degree in Computer Science and Artificial Intelligence, specializing in Information Technology. I enjoy transforming ideas into reliable, production-ready mobile applications by applying Clean Architecture, SOLID principles, and modern development practices. Through professional training at the Digital Egypt Pioneers Initiative (DEPI) and the National Telecommunication Institute (NTI), I've gained hands-on experience developing scalable Flutter applications, integrating Firebase and REST APIs, and collaborating with teams using Git and agile workflows. I've built and maintained 10+ production-ready applications, developed 100+ responsive mobile screens, and integrated 50+ backend APIs. I'm passionate about writing clean, maintainable code and continuously learning new technologies to create software that solves real-world problems.</t>
+  </si>
+  <si>
+    <t>assets/cv/Ahmed Nasr Makled Flutter App Developer CV.pdf</t>
   </si>
 </sst>
 </file>
@@ -458,7 +458,7 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D1" t="s">
         <v>2</v>
@@ -496,13 +496,13 @@
         <v>11</v>
       </c>
       <c r="C2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D2" t="s">
         <v>12</v>
       </c>
       <c r="E2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F2" t="s">
         <v>13</v>
@@ -517,7 +517,7 @@
         <v>15</v>
       </c>
       <c r="J2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="K2" t="s">
         <v>16</v>
